--- a/out/LSTM_Base_repeat_2_000008.xlsx
+++ b/out/LSTM_Base_repeat_2_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.501156825476262</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.501156825476262</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.501156825476262</v>
+        <v>9.227858435864231</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.331760215741336</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.931760215741336</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001303766775417607</v>
+        <v>-8.814955669618211e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1497777613463098</v>
+        <v>-0.1012669099610395</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1500345708966141</v>
+        <v>-0.1014331470223259</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4546235598082852</v>
+        <v>0.280784626064627</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.760085957081418</v>
+        <v>0.4606757363498385</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03239186977169738</v>
+        <v>0.0200058822409753</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3695163564097788</v>
+        <v>0.2194519510909577</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05680430298562478</v>
+        <v>0.03508337270451147</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4507222826902114</v>
+        <v>0.2696063947709515</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06901020780605491</v>
+        <v>0.042622466309079</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.531933614505851</v>
+        <v>0.31976435981928</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01826199506291252</v>
+        <v>0.01127882762152322</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4993586646931732</v>
+        <v>0.2996452760272641</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01014526341523565</v>
+        <v>0.006264118489158451</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5013702006707734</v>
+        <v>0.3008857286902564</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02131691151378321</v>
+        <v>0.01316483409892891</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5338714421738915</v>
+        <v>0.320958103300164</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008371996259383377</v>
+        <v>0.005168706523071533</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.529279783218364</v>
+        <v>0.3181203424127828</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005959825697429417</v>
+        <v>0.003679461448730259</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5328256739849266</v>
+        <v>0.3203084030693702</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002342793882804033</v>
+        <v>0.001445227800367095</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.531546426268184</v>
+        <v>0.3195165296815226</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001328322389463191</v>
+        <v>0.0008181146311830566</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5318575504039875</v>
+        <v>0.3197066860844351</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005023275076545038</v>
+        <v>0.0003085565845920197</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5315339923064129</v>
+        <v>0.319505026608557</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002328074557778932</v>
+        <v>0.0001414277389743509</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5314968453412594</v>
+        <v>0.3194802041705244</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.219113179022926e-05</v>
+        <v>4.909079472171628e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5314279266746735</v>
+        <v>0.3194357333050648</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.075723058958612e-05</v>
+        <v>1.074052980474707e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.531386836193525</v>
+        <v>0.3194085493913081</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.878615294793062e-06</v>
+        <v>3.108757778203038e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.53138181608819</v>
+        <v>0.3194035367323935</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.191662034084867e-06</v>
+        <v>-8.904788376657899e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5313778340035979</v>
+        <v>0.3193991551468328</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5313753993334072</v>
+        <v>0.3193958047920401</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5313698820914174</v>
+        <v>0.3193904354650522</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5313635580974095</v>
+        <v>0.3193844427316219</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5313581903088311</v>
+        <v>0.3193790749430435</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5313582270573228</v>
+        <v>0.3193791116915352</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5313583373027984</v>
+        <v>0.3193792219370107</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5313584107997821</v>
+        <v>0.3193792954339944</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5313585945422412</v>
+        <v>0.3193794791764535</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5313601379788977</v>
+        <v>0.31938102261311</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5313616079185708</v>
+        <v>0.3193824925527831</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5313628573672927</v>
+        <v>0.3193837420015051</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5313642170614901</v>
+        <v>0.3193851016957024</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5313620121519808</v>
+        <v>0.3193828967861931</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5313616079185708</v>
+        <v>0.3193824925527831</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5313607627032588</v>
+        <v>0.3193816473374712</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.531361313930636</v>
+        <v>0.3193821985648484</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5313609831942097</v>
+        <v>0.319381867828422</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5313606892062751</v>
+        <v>0.3193815738404875</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5313607627032588</v>
+        <v>0.3193816473374712</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5313603217213568</v>
+        <v>0.3193812063555692</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5313602114758813</v>
+        <v>0.3193810961100936</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5313601747273896</v>
+        <v>0.3193810593616019</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5313603217213568</v>
+        <v>0.3193812063555692</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5313598439909631</v>
+        <v>0.3193807286251755</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5313607994517505</v>
+        <v>0.3193816840859628</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5313607627032588</v>
+        <v>0.3193816473374712</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5313604319668324</v>
+        <v>0.3193813166010447</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5313608729487344</v>
+        <v>0.3193817575829467</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5313602482243732</v>
+        <v>0.3193811328585855</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5313600644819141</v>
+        <v>0.3193809491161264</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.531359660248504</v>
+        <v>0.3193805448827164</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.531358815033192</v>
+        <v>0.3193796996674044</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5313587782847004</v>
+        <v>0.3193796629189127</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5313589252786676</v>
+        <v>0.31937980991288</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.531358851781684</v>
+        <v>0.3193797364158963</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5313589252786676</v>
+        <v>0.31937980991288</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5313589620271595</v>
+        <v>0.3193798466613719</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.531358851781684</v>
+        <v>0.3193797364158963</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.531359292763586</v>
+        <v>0.3193801773977983</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5313591825181104</v>
+        <v>0.3193800671523228</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5313591457696184</v>
+        <v>0.3193800304038308</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5313590722726348</v>
+        <v>0.3193799569068472</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5313590355241431</v>
+        <v>0.3193799201583555</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.531358815033192</v>
+        <v>0.3193796996674044</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5313587415362084</v>
+        <v>0.3193796261704208</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5313586680392248</v>
+        <v>0.3193795526734372</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5313587047877167</v>
+        <v>0.3193795894219291</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5313585945422412</v>
+        <v>0.3193794791764535</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5313587047877167</v>
+        <v>0.3193795894219291</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5313589987756512</v>
+        <v>0.3193798834098636</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_2_000008.xlsx
+++ b/out/LSTM_Base_repeat_2_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.331760215741336</v>
+        <v>0.4313973956586084</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586084</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.01612649947684264</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586084</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586082</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.01612649947684264</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.331760215741336</v>
+        <v>0.4313973956586084</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.331760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001303766775417607</v>
+        <v>-0.0001246097931289114</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1497777613463098</v>
+        <v>-0.1431527187882035</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1432773285813324</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.331760215741336</v>
+        <v>0.4313973956586084</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1432773285813324</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768428</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1432773285813324</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1432773285813324</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1432773285813324</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1432773285813324</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1432773285813324</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768428</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1432773285813324</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.331760215741336</v>
+        <v>0.4313973956586081</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1432773285813324</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1432773285813324</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1432773285813324</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1432773285813324</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1499081380238517</v>
+        <v>-0.1432773285813324</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1500345708966141</v>
+        <v>-0.1433906392786013</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4546235598082852</v>
+        <v>0.4074392051853107</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.760085957081418</v>
+        <v>0.6722705837647742</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03239186977169738</v>
+        <v>0.02902995782517951</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3695163564097788</v>
+        <v>0.3222372760416712</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05680430298562478</v>
+        <v>0.05090878322550219</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4507222826902114</v>
+        <v>0.3950151234995096</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06901020780605491</v>
+        <v>0.06184784755286434</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.331760215741336</v>
+        <v>0.4313973956586084</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.531933614505851</v>
+        <v>0.467797815530723</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01826199506291252</v>
+        <v>0.01636665508556895</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.501156825476262</v>
+        <v>0.4313973956586081</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4993586646931732</v>
+        <v>0.4386036904541831</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01014526341523565</v>
+        <v>0.009091972264581751</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.331760215741336</v>
+        <v>0.4313973956586081</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5013702006707734</v>
+        <v>0.4404059378928274</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02131691151378321</v>
+        <v>0.01910416863870784</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.331760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5338714421738915</v>
+        <v>0.4695334781671993</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008371996259383377</v>
+        <v>0.007502445397125568</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.931760215741336</v>
+        <v>1.078921290794059</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.529279783218364</v>
+        <v>0.4654179246229869</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005959825697429417</v>
+        <v>0.005340573983902188</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586082</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5328256739849266</v>
+        <v>0.4685952251387467</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002342793882804033</v>
+        <v>0.002099731358210672</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768428</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.531546426268184</v>
+        <v>0.4674482272443988</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001328322389463191</v>
+        <v>0.001189595204432339</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5318575504039875</v>
+        <v>0.4677264598516214</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005023275076545038</v>
+        <v>0.0004494808922738263</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5315339923064129</v>
+        <v>0.4674360466095319</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002328074557778932</v>
+        <v>0.0002085863260227374</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5314968453412594</v>
+        <v>0.4674022398834902</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.219113179022926e-05</v>
+        <v>7.331055355233552e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5314279266746735</v>
+        <v>0.4673400954961831</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.075723058958612e-05</v>
+        <v>1.789531607963211e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.531386836193525</v>
+        <v>0.4673029783200037</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.878615294793062e-06</v>
+        <v>6.447658039816054e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.53138181608819</v>
+        <v>0.4672979604485948</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.191662034084867e-06</v>
+        <v>1.164281743501315e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5313778340035979</v>
+        <v>0.4672938696960076</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5313753993334072</v>
+        <v>0.4672912522925888</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5313698820914174</v>
+        <v>0.4672857350505991</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5313635580974095</v>
+        <v>0.4672794110565912</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5313581903088311</v>
+        <v>0.4672740432680128</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5313582270573228</v>
+        <v>0.4672740800165045</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5313583373027984</v>
+        <v>0.46727419026198</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.01612649947684275</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5313584107997821</v>
+        <v>0.4672742637589637</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586082</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5313585945422412</v>
+        <v>0.4672744475014228</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5313601379788977</v>
+        <v>0.4672759909380793</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5313616079185708</v>
+        <v>0.4672774608777524</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5313628573672927</v>
+        <v>0.4672787103264744</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5313642170614901</v>
+        <v>0.4672800700206717</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586082</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5313620121519808</v>
+        <v>0.4672778651111624</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.0161264994768428</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5313616079185708</v>
+        <v>0.4672774608777524</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5313607627032588</v>
+        <v>0.4672766156624404</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.531361313930636</v>
+        <v>0.4672771668898177</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5313609831942097</v>
+        <v>0.4672768361533913</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5313606892062751</v>
+        <v>0.4672765421654568</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5313607627032588</v>
+        <v>0.4672766156624404</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5313603217213568</v>
+        <v>0.4672761746805385</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5313602114758813</v>
+        <v>0.4672760644350629</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5313601747273896</v>
+        <v>0.4672760276865712</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5313603217213568</v>
+        <v>0.4672761746805385</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.01612649947684275</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5313598439909631</v>
+        <v>0.4672756969501448</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.01612649947684275</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5313607994517505</v>
+        <v>0.4672766524109321</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.01612649947684275</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5313607627032588</v>
+        <v>0.4672766156624404</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.6636503946122936</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5313604319668324</v>
+        <v>0.467276284926014</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.6636503946122936</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5313608729487344</v>
+        <v>0.467276725907916</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5313602482243732</v>
+        <v>0.4672761011835548</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5313600644819141</v>
+        <v>0.4672759174410957</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.531359660248504</v>
+        <v>0.4672755132076857</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.531358815033192</v>
+        <v>0.4672746679923737</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5313587782847004</v>
+        <v>0.467274631243882</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5313589252786676</v>
+        <v>0.4672747782378492</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.531358851781684</v>
+        <v>0.4672747047408656</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5313589252786676</v>
+        <v>0.4672747782378492</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5313589620271595</v>
+        <v>0.4672748149863412</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.531358851781684</v>
+        <v>0.4672747047408656</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.531359292763586</v>
+        <v>0.4672751457227676</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5313591825181104</v>
+        <v>0.467275035477292</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5313591457696184</v>
+        <v>0.4672749987288001</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5313590722726348</v>
+        <v>0.4672749252318165</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5313590355241431</v>
+        <v>0.4672748884833248</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.531358815033192</v>
+        <v>0.4672746679923737</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5313587415362084</v>
+        <v>0.46727459449539</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5313586680392248</v>
+        <v>0.4672745209984064</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5313587047877167</v>
+        <v>0.4672745577468984</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.01612649947684275</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5313585945422412</v>
+        <v>0.4672744475014228</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586082</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5313587047877167</v>
+        <v>0.4672745577468984</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5313589987756512</v>
+        <v>0.4672748517348329</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_2_000008.xlsx
+++ b/out/LSTM_Base_repeat_2_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.02157554775476456</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.01282681711018085</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.5799999999999996</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.0004159864038228989</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.16</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.008008323609828949</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.4313973956586084</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.00267953984439373</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.6313973956586084</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.003810584545135498</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.01612649947684264</v>
+        <v>0.16</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.005621626973152161</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.006262762472033501</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.004559488967061043</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.003945911303162575</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.001894937828183174</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.0005514435470104218</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.2161264994768426</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.0002270061522722244</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.6313973956586084</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.0006842371076345444</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.003777187317609787</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.278921290794059</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.001945594325661659</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.6313973956586082</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.001010162755846977</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.01612649947684264</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.002291908487677574</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.002316722646355629</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.001654576510190964</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.16</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.001281920820474625</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.0004535894840955734</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.2161264994768427</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>2.548471093177795e-05</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.4313973956586084</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.001722067594528198</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.001738088205456734</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.001160319894552231</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.0005225781351327896</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.0007481519132852554</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.001770716160535812</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.0032673180103302</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01010193675756454</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.007096216082572937</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.003756849095225334</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.078921290794059</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.002283260226249695</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.078921290794059</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.0006435345858335495</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.001449842005968094</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.16</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.0009925160557031631</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.16</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.0006522703915834427</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.003233559429645538</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.078921290794059</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.005685906857252121</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.078921290794059</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.006201598793268204</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.078921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.008480232208967209</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.078921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01420152187347412</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.078921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.01696299389004707</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.078921290794059</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001246097931289114</v>
+        <v>-0.0001164229180378607</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1431527187882035</v>
+        <v>-0.1337475717430304</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.006741881370544434</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.16</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1432773285813324</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.001584975048899651</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.4313973956586084</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1432773285813324</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.004855791106820107</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.2161264994768428</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1432773285813324</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.006616970524191856</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1432773285813324</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.006951672956347466</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1432773285813324</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.005957845598459244</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1432773285813324</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.004513256251811981</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1432773285813324</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.001428715884685516</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.2161264994768428</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1432773285813324</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>5.756504833698273e-05</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.4313973956586081</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1432773285813324</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.001173930242657661</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.278921290794059</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1432773285813324</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.001510865986347198</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.278921290794059</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1432773285813324</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.001550033688545227</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.278921290794059</v>
+        <v>0.16</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1432773285813324</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.002873815596103668</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.278921290794059</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1432773285813324</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.008019275963306427</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.278921290794059</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1433906392786013</v>
+        <v>-0.1339632802291097</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4074392051853107</v>
+        <v>0.3570080345747745</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.005202924832701683</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.278921290794059</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6722705837647742</v>
+        <v>0.580738771898895</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02902995782517951</v>
+        <v>0.02543674750750171</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.003156229853630066</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.278921290794059</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3222372760416712</v>
+        <v>0.274031111284032</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05090878322550219</v>
+        <v>0.04460751661091531</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.004893094301223755</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.278921290794059</v>
+        <v>0.3</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3950151234995096</v>
+        <v>0.3378008349680961</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06184784755286434</v>
+        <v>0.05419286457635664</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.001641755923628807</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.4313973956586084</v>
+        <v>0.16</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.467797815530723</v>
+        <v>0.4015748030810274</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01636665508556895</v>
+        <v>0.01434062476676132</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.003392212092876434</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.4313973956586081</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4386036904541831</v>
+        <v>0.3759943284802746</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.009091972264581751</v>
+        <v>0.007966040344917233</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.004730308428406715</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.4313973956586081</v>
+        <v>-0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4404059378928274</v>
+        <v>0.3775728929704919</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01910416863870784</v>
+        <v>0.01673887594146502</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.008870340883731842</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4695334781671993</v>
+        <v>0.4030953199304976</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007502445397125568</v>
+        <v>0.00657355192727635</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.007013667374849319</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.078921290794059</v>
+        <v>-0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4654179246229869</v>
+        <v>0.3994883636710751</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005340573983902188</v>
+        <v>0.004679923827130798</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.0004786532372236252</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.6313973956586082</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4685952251387467</v>
+        <v>0.4022719183261736</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002099731358210672</v>
+        <v>0.001839016248032318</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.002012161538004875</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.2161264994768428</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4674482272443988</v>
+        <v>0.4012663808161579</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001189595204432339</v>
+        <v>0.00104161954039943</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.005955751985311508</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4677264598516214</v>
+        <v>0.4015095291262278</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004494808922738263</v>
+        <v>0.0003931111692011037</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.009085331112146378</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4674360466095319</v>
+        <v>0.4012544703966556</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002085863260227374</v>
+        <v>0.0001821632753807493</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.01142128929495811</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4674022398834902</v>
+        <v>0.4012242273892998</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.331055355233552e-05</v>
+        <v>6.362265002008783e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.01198177877813578</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4673400954961831</v>
+        <v>0.4011691524107316</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.789531607963211e-05</v>
+        <v>1.503340156967809e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.01076956745237112</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4673029783200037</v>
+        <v>0.4011360085395214</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>6.447658039816054e-06</v>
+        <v>5.016700784839047e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.008955486118793488</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4672979604485948</v>
+        <v>0.4011309929020386</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.164281743501315e-06</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.005127860233187675</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4672938696960076</v>
+        <v>0.4011267926927162</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-8.167273192660964e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.004534492269158363</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4672912522925888</v>
+        <v>0.4011238088136106</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.004815543070435524</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4672857350505991</v>
+        <v>0.4011183650686043</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.005864394828677177</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4672794110565912</v>
+        <v>0.4011123723351739</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.005294026806950569</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4672740432680128</v>
+        <v>0.4011070045465955</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.004306759685277939</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4672740800165045</v>
+        <v>0.4011070412950872</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.002455225214362144</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.46727419026198</v>
+        <v>0.4011071515405628</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.001733498647809029</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.01612649947684275</v>
+        <v>0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4672742637589637</v>
+        <v>0.4011072250375464</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.004516679793596268</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.6313973956586082</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4672744475014228</v>
+        <v>0.4011074087800055</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.01471195369958878</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.278921290794059</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4672759909380793</v>
+        <v>0.401108952216662</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.01522801071405411</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4672774608777524</v>
+        <v>0.4011104221563351</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.01621477678418159</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4672787103264744</v>
+        <v>0.4011116716050571</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.02696094289422035</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.278921290794059</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4672800700206717</v>
+        <v>0.4011130312992544</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.00687631219625473</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.6313973956586082</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4672778651111624</v>
+        <v>0.4011108263897451</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.006435373798012733</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.0161264994768428</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4672774608777524</v>
+        <v>0.4011104221563351</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.01470149122178555</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4672766156624404</v>
+        <v>0.4011095769410231</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.02013085037469864</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4672771668898177</v>
+        <v>0.4011101281684004</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.021873963996768</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4672768361533913</v>
+        <v>0.4011097974319739</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.01869599893689156</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4672765421654568</v>
+        <v>0.4011095034440395</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.01786713302135468</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4672766156624404</v>
+        <v>0.4011095769410231</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.01713284105062485</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4672761746805385</v>
+        <v>0.4011091359591212</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.01535194553434849</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4672760644350629</v>
+        <v>0.4011090257136456</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.01153733022511005</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4672760276865712</v>
+        <v>0.4011089889651539</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.01114247366786003</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.16</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4672761746805385</v>
+        <v>0.4011091359591212</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.001279605552554131</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.01612649947684275</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4672756969501448</v>
+        <v>0.4011086582287275</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.005371233448386192</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.01612649947684275</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4672766524109321</v>
+        <v>0.4011096136895148</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.003462174907326698</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.01612649947684275</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4672766156624404</v>
+        <v>0.4011095769410231</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.009058397263288498</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6636503946122936</v>
+        <v>0.16</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.467276284926014</v>
+        <v>0.4011092462045967</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.01180492155253887</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6636503946122936</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.467276725907916</v>
+        <v>0.4011096871864986</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.01427451614290476</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4672761011835548</v>
+        <v>0.4011090624621376</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.01502607483416796</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4672759174410957</v>
+        <v>0.4011088787196784</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.01661492139101028</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4672755132076857</v>
+        <v>0.4011084744862684</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.01739142462611198</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4672746679923737</v>
+        <v>0.4011076292709564</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.01475758757442236</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.467274631243882</v>
+        <v>0.4011075925224647</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.01125901937484741</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4672747782378492</v>
+        <v>0.4011077395164319</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.008493725210428238</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4672747047408656</v>
+        <v>0.4011076660194483</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.001098219305276871</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4672747782378492</v>
+        <v>0.4011077395164319</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.003816885873675346</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4672748149863412</v>
+        <v>0.4011077762649238</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.001683695241808891</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4672747047408656</v>
+        <v>0.4011076660194483</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.003526551648974419</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4672751457227676</v>
+        <v>0.4011081070013502</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.003916367888450623</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.467275035477292</v>
+        <v>0.4011079967558747</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.005491582676768303</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4672749987288001</v>
+        <v>0.4011079600073828</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.005785012617707253</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4672749252318165</v>
+        <v>0.4011078865103992</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.006398782134056091</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4672748884833248</v>
+        <v>0.4011078497619075</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.007553014904260635</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4672746679923737</v>
+        <v>0.4011076292709564</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.006004786118865013</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.16</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.46727459449539</v>
+        <v>0.4011075557739728</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.005561234429478645</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4672745209984064</v>
+        <v>0.4011074822769892</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.005346802994608879</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4672745577468984</v>
+        <v>0.4011075190254811</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.003615120425820351</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.01612649947684275</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4672744475014228</v>
+        <v>0.4011074087800055</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
+        <v>0.001360548660159111</v>
+      </c>
+      <c r="JB125" t="n">
         <v>1</v>
       </c>
-      <c r="JB125" t="n">
-        <v>0.6313973956586082</v>
-      </c>
       <c r="JC125" t="n">
-        <v>0.4672745577468984</v>
+        <v>0.4011075190254811</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.003446292132139206</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.278921290794059</v>
+        <v>1.14</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4672748517348329</v>
+        <v>0.4011078130134155</v>
       </c>
     </row>
   </sheetData>
